--- a/htr-ML-Sections/ig/StructureDefinition-fr-cda-authenticator.xlsx
+++ b/htr-ML-Sections/ig/StructureDefinition-fr-cda-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T12:47:35+00:00</t>
+    <t>2026-05-07T13:30:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-ML-Sections/ig/StructureDefinition-fr-cda-authenticator.xlsx
+++ b/htr-ML-Sections/ig/StructureDefinition-fr-cda-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T13:30:39+00:00</t>
+    <t>2026-05-12T13:21:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
